--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research Projects\Frank Chapter 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81B66F1-05B3-406C-9602-7534447A4455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FFD49C-95FF-43B8-871F-CDD6D112D069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C3A83ADC-0783-41F6-A5A4-36106CF2313C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="251">
   <si>
     <t>Dataset Variable</t>
   </si>
@@ -769,6 +769,15 @@
   </si>
   <si>
     <t>hourly minimum wage received by workers from primary job. Defined as real_salary_income_wage_primary / (52/12 * eff_weekly_hours). This uses the overtime adjusted hours worked and weeks per month (52/12) to convert monthly salary earned to hourly.</t>
+  </si>
+  <si>
+    <t>salary_income_all_primary</t>
+  </si>
+  <si>
+    <t>INGRESO_ASALARIADO + INGRESO_INDEPENDIENTES</t>
+  </si>
+  <si>
+    <t>value of salary and independent earnings.</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8355F2E2-0331-403D-87E2-9A1B3F820AFC}">
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -1639,45 +1648,25 @@
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>117</v>
       </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" t="s">
-        <v>118</v>
-      </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
@@ -1691,16 +1680,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1715,16 +1704,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1742,13 +1731,13 @@
     <row r="30" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1765,30 +1754,42 @@
     </row>
     <row r="31" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="C31" s="3"/>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
-      <c r="B32" t="s">
-        <v>164</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D32" t="s">
-        <v>166</v>
-      </c>
+      <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>248</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>89</v>
+        <v>249</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>250</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -1806,37 +1807,25 @@
     <row r="34" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H34" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -1851,16 +1840,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -1877,95 +1866,95 @@
     </row>
     <row r="37" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>9</v>
+      </c>
+      <c r="G37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" t="s">
+        <v>125</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" t="s">
         <v>91</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" t="s">
-        <v>10</v>
-      </c>
-      <c r="H38" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C40" s="3"/>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B43" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D43" t="s">
         <v>79</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" t="s">
-        <v>10</v>
-      </c>
-      <c r="H41" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
-      <c r="B42" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D42" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" t="s">
-        <v>10</v>
-      </c>
-      <c r="H42" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D43" t="s">
-        <v>81</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -1983,13 +1972,13 @@
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D44" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2007,13 +1996,13 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D45" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2031,13 +2020,13 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D46" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2055,13 +2044,13 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2077,71 +2066,71 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C48" s="3"/>
+      <c r="A48" s="5"/>
+      <c r="B48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C49" s="3"/>
+      <c r="A49" s="5"/>
+      <c r="B49" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B52" t="s">
         <v>126</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D52" t="s">
         <v>148</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>9</v>
-      </c>
-      <c r="G50" t="s">
-        <v>10</v>
-      </c>
-      <c r="H50" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="5"/>
-      <c r="B51" t="s">
-        <v>127</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D51" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G51" t="s">
-        <v>10</v>
-      </c>
-      <c r="H51" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="5"/>
-      <c r="B52" t="s">
-        <v>128</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D52" t="s">
-        <v>147</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2159,13 +2148,13 @@
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="D53" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2183,13 +2172,13 @@
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" t="s">
-        <v>130</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>137</v>
+        <v>128</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="D54" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2201,23 +2190,43 @@
         <v>10</v>
       </c>
       <c r="H54" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
-      <c r="C55" s="4"/>
+      <c r="B55" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s">
+        <v>10</v>
+      </c>
+      <c r="H55" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" t="s">
-        <v>131</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>94</v>
+        <v>130</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="D56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2234,38 +2243,18 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
-      <c r="B57" t="s">
-        <v>132</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D57" t="s">
-        <v>152</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>9</v>
-      </c>
-      <c r="G57" t="s">
-        <v>10</v>
-      </c>
-      <c r="H57" t="s">
-        <v>100</v>
-      </c>
+      <c r="C57" s="4"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D58" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2283,13 +2272,13 @@
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D59" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2304,35 +2293,65 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" t="s">
+        <v>153</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>9</v>
+      </c>
+      <c r="G60" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="5"/>
+      <c r="B61" t="s">
+        <v>134</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61" t="s">
+        <v>154</v>
+      </c>
+      <c r="E61" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" t="s">
+        <v>9</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5"/>
+      <c r="B62" t="s">
         <v>135</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C62" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D62" t="s">
         <v>155</v>
       </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>9</v>
-      </c>
-      <c r="G60" t="s">
-        <v>10</v>
-      </c>
-      <c r="H60" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C61" s="3"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C62" s="3"/>
       <c r="E62" t="s">
         <v>8</v>
       </c>
@@ -2347,65 +2366,35 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C64" s="3"/>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G64" t="s">
+        <v>10</v>
+      </c>
+      <c r="H64" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B65" t="s">
         <v>182</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D65" t="s">
         <v>184</v>
-      </c>
-      <c r="E63" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" t="s">
-        <v>9</v>
-      </c>
-      <c r="G63" t="s">
-        <v>10</v>
-      </c>
-      <c r="H63" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="5"/>
-      <c r="B64" t="s">
-        <v>139</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D64" t="s">
-        <v>172</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>9</v>
-      </c>
-      <c r="G64" t="s">
-        <v>10</v>
-      </c>
-      <c r="H64" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="5"/>
-      <c r="B65" t="s">
-        <v>138</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D65" t="s">
-        <v>173</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -2423,13 +2412,13 @@
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D66" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -2444,16 +2433,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D67" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -2468,16 +2457,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
       <c r="B68" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D68" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -2492,20 +2481,40 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
-      <c r="C69" s="3"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D69" t="s">
+        <v>175</v>
+      </c>
+      <c r="E69" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G69" t="s">
+        <v>10</v>
+      </c>
+      <c r="H69" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
       <c r="B70" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -2520,40 +2529,20 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
-      <c r="B71" t="s">
-        <v>162</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D71" t="s">
-        <v>177</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>9</v>
-      </c>
-      <c r="G71" t="s">
-        <v>10</v>
-      </c>
-      <c r="H71" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
       <c r="B72" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="D72" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -2568,16 +2557,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
       <c r="B73" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D73" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -2592,16 +2581,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D74" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -2616,16 +2605,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
       <c r="B75" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D75" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -2640,19 +2629,40 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>144</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D76" t="s">
+        <v>180</v>
+      </c>
+      <c r="E76" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" t="s">
+        <v>9</v>
+      </c>
+      <c r="G76" t="s">
+        <v>10</v>
+      </c>
+      <c r="H76" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>145</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -2669,38 +2679,17 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
-      <c r="B78" t="s">
-        <v>199</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D78" t="s">
-        <v>202</v>
-      </c>
-      <c r="E78" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" t="s">
-        <v>9</v>
-      </c>
-      <c r="G78" t="s">
-        <v>10</v>
-      </c>
-      <c r="H78" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" t="s">
-        <v>193</v>
-      </c>
-      <c r="C79" t="s">
-        <v>190</v>
+        <v>192</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="D79" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -2715,16 +2704,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
       <c r="B80" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -2741,17 +2730,38 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>193</v>
+      </c>
+      <c r="C81" t="s">
+        <v>190</v>
+      </c>
+      <c r="D81" t="s">
+        <v>200</v>
+      </c>
+      <c r="E81" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
       <c r="B82" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D82" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -2768,261 +2778,288 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
-      <c r="B83" t="s">
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="5"/>
+      <c r="B84" t="s">
+        <v>198</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D84" t="s">
+        <v>204</v>
+      </c>
+      <c r="E84" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" t="s">
+        <v>9</v>
+      </c>
+      <c r="G84" t="s">
+        <v>10</v>
+      </c>
+      <c r="H84" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="5"/>
+      <c r="B85" t="s">
         <v>195</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D85" t="s">
         <v>205</v>
       </c>
-      <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>9</v>
-      </c>
-      <c r="G83" t="s">
-        <v>10</v>
-      </c>
-      <c r="H83" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
+      <c r="E85" t="s">
+        <v>8</v>
+      </c>
+      <c r="F85" t="s">
+        <v>9</v>
+      </c>
+      <c r="G85" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B88" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="5"/>
-      <c r="B87" t="s">
-        <v>211</v>
-      </c>
-      <c r="C87" s="3"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="5"/>
-      <c r="B88" t="s">
-        <v>206</v>
-      </c>
-      <c r="C88" s="3"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
+      <c r="B89" t="s">
+        <v>211</v>
+      </c>
+      <c r="C89" s="3"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
       <c r="B90" t="s">
-        <v>207</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C90" s="3"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
-      <c r="B91" t="s">
-        <v>208</v>
-      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
+      <c r="B93" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
       <c r="B94" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
-      <c r="B95" t="s">
-        <v>216</v>
-      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
+      <c r="B97" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
       <c r="B98" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
-      <c r="B99" t="s">
-        <v>213</v>
-      </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
       <c r="B100" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="5"/>
+      <c r="B101" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="5"/>
+      <c r="B102" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B105" t="s">
         <v>218</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="5"/>
-      <c r="B104" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="5"/>
-      <c r="B105" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
+      <c r="B106" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
       <c r="B107" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
-      <c r="B108" t="s">
-        <v>222</v>
-      </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
       <c r="B109" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="5"/>
+      <c r="B110" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="5"/>
+      <c r="B111" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>226</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B114" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B113" t="s">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B114" t="s">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B115" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B119" t="s">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
         <v>236</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C121" t="s">
         <v>237</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D121" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B120" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
         <v>235</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D122" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B122" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
         <v>232</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D124" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B123" t="s">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
         <v>241</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D125" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
         <v>234</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D126" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B126" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
         <v>231</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D128" t="s">
         <v>239</v>
       </c>
-      <c r="F126" t="s">
+      <c r="F128" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B127" t="s">
+    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
         <v>233</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D129" t="s">
         <v>244</v>
       </c>
-      <c r="F127" t="s">
+      <c r="F129" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B128" t="s">
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B133" t="s">
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
         <v>234</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A63:A83"/>
-    <mergeCell ref="A86:A100"/>
-    <mergeCell ref="A103:A109"/>
+    <mergeCell ref="A65:A85"/>
+    <mergeCell ref="A88:A102"/>
+    <mergeCell ref="A105:A111"/>
     <mergeCell ref="A2:A23"/>
-    <mergeCell ref="A26:A38"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="A50:A60"/>
+    <mergeCell ref="A27:A40"/>
+    <mergeCell ref="A43:A49"/>
+    <mergeCell ref="A52:A62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
